--- a/results/07-2026/beta/inputs-comparison-07-2026.xlsx
+++ b/results/07-2026/beta/inputs-comparison-07-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t xml:space="preserve">consumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uncertainty</t>
   </si>
   <si>
     <t xml:space="preserve">federal_purchases</t>
@@ -757,13 +760,16 @@
       <c r="AY1" t="s">
         <v>50</v>
       </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -793,41 +799,41 @@
         <v>14503.1</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>1460.3</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>212.211</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>75.79</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>2481.8</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>3391.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>1889</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>192.5</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
         <v>63.5</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1571.2</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>154.2</v>
       </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
@@ -835,14 +841,14 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
         <v>39.2</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>80</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
@@ -853,35 +859,35 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0.6</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>1228.089</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>183.511</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>-1961.394</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>-1109.886</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>-88.1233333333332</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>-25.3166666666666</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>1374.885</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>135.765</v>
       </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
@@ -889,14 +895,14 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
         <v>28.143</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>30.366</v>
       </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
@@ -904,21 +910,24 @@
         <v>0</v>
       </c>
       <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
         <v>0.2664</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AY2" t="n">
         <v>1094.7726</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AZ2" t="n">
         <v>178.1649</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -948,132 +957,135 @@
         <v>13193.3</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>1567.7</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>321.194</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>75.484</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>2454</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>3135.5</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>1797.5</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>199.7</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
       <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>68.5</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>1649.3</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>156.6</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>1078.1</v>
       </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
         <v>779.6</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>170.2</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>1031.8</v>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
         <v>160.9</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
       <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
         <v>45</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>0.6</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>1326.164</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>149.436</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
         <v>-1950.966</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>-1107.138</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>-87.2566666666666</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>-25.8066666666666</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
         <v>1407.15</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>137.7225</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>264.1345</v>
       </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
         <v>245.574</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>73.3005</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
         <v>78.291</v>
       </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
         <v>9</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>0.2673</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
         <v>1122.5529</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AZ3" t="n">
         <v>166.7421</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
         <v>-1</v>
@@ -1103,132 +1115,135 @@
         <v>14479.2</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>1528.7</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>296.718</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>79.305</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>2473.2</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3319.2</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1924.5</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>257.7</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
       <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>81.6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>1803.8</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>159.6</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>15.6</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
       <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
         <v>688.6</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>112.4</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>1163.3</v>
       </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
       <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
         <v>58.4</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
       <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>45</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>0.6</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>1320.282</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>205.818</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>-1957.164</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>-1117.866</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>-87.7966666666666</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>-26.72</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>1472.6475</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>139.9275</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>117.0225</v>
       </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
         <v>462.483</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>97.3665</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>126.1278</v>
       </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
         <v>16.65</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>0.2682</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
         <v>1145.862</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AZ4" t="n">
         <v>167.2155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
         <v>-1</v>
@@ -1258,132 +1273,135 @@
         <v>14749.8</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1541.6</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>291.474</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>75.888</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>2489.2</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3478.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>1961.9</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>251</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>78.2</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>1687.1</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>162.3</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>5</v>
       </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
       <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
         <v>252.5</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>69.5</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>516.4</v>
       </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
       <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
         <v>34.5</v>
       </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
       <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
         <v>45</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>0.6</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>1355.226</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>171.374</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
         <v>-1995.864</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>-1138.026</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
         <v>-88.0833333333332</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AM5" t="n">
         <v>-27.51</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
         <v>1510.065</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AO5" t="n">
         <v>142.3575</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AP5" t="n">
         <v>63.2366</v>
       </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
         <v>366.6105</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
         <v>78.534</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
         <v>138.8241</v>
       </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
         <v>23.85</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AX5" t="n">
         <v>0.2691</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
         <v>1176.696225</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AZ5" t="n">
         <v>159.781275</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
         <v>-1</v>
@@ -1413,132 +1431,135 @@
         <v>15255.4</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1616.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>318.381</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>73.446</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2538.7</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3641.3</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>2012.3</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>280</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
       <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>81.6</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>1948.8</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>165.9</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>585.6</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>1348.1</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>499.2</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>89.3</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>534.3</v>
       </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
       <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
         <v>21.4</v>
       </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
       <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>45</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AG6" t="n">
         <v>2.5</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
         <v>1363.119</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AI6" t="n">
         <v>205.081</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AJ6" t="n">
         <v>-2038.506</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AK6" t="n">
         <v>-1154.364</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AL6" t="n">
         <v>-90.2333333333332</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AM6" t="n">
         <v>-28.4</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AN6" t="n">
         <v>1595.025</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AO6" t="n">
         <v>144.99</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
         <v>205.2442</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AQ6" t="n">
         <v>188.734</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
         <v>368.9235</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
         <v>78.4215</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
         <v>154.4499</v>
       </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
       <c r="AU6" t="n">
         <v>0</v>
       </c>
       <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
         <v>30.6</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AX6" t="n">
         <v>0.36405</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AY6" t="n">
         <v>1207.077975</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
         <v>164.634525</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
         <v>-1</v>
@@ -1568,132 +1589,135 @@
         <v>16027.6</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1597.4</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>355.565</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>74.11</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>2576.9</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3796.8</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>2119.2</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>339.3</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
       <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>99.6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>1749.37816</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>169.2</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>290.1</v>
       </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
       <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>402.1</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>35.4</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>838.2</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>58.78296</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>13.3</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>33.92184</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>45</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>8.6</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
         <v>1404.179</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AI7" t="n">
         <v>220.221</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AJ7" t="n">
         <v>-2089.86</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AK7" t="n">
         <v>-1176.786</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AL7" t="n">
         <v>-93.9066666666666</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AM7" t="n">
         <v>-29.7066666666666</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
         <v>1617.542586</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>147.825</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
         <v>194.0897</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>134.81</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
         <v>379.138</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>69.91</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
         <v>181.962225</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>2.3513184</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>6.78436800000001</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
         <v>34.65</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AX7" t="n">
         <v>0.747225</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
         <v>1224.63135</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="AZ7" t="n">
         <v>180.56115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
         <v>-1</v>
@@ -1723,132 +1747,135 @@
         <v>16380.7</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1585.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>374.239</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>70.133</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>2634.6</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>3918.9</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>2124.1</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>348.7</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
       <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>123.7</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>1919.22984</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>174.5</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>38.9</v>
       </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
       <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
         <v>207.6</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-4.6</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>689.7</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>267.78904</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>21.804</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>44.96616</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>45</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AH8" t="n">
         <v>1437.905</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
         <v>205.295</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
         <v>-2144.436</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AK8" t="n">
         <v>-1197.36</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AL8" t="n">
         <v>-98.0133333333332</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
         <v>-31.7766666666666</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
         <v>1643.5143</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>151.1775</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AP8" t="n">
         <v>134.3118</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AQ8" t="n">
         <v>134.81</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
         <v>328.578</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
         <v>51.465</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
         <v>200.71755</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>13.06288</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>14.7599448</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>36.9</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AX8" t="n">
         <v>0.6939</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AY8" t="n">
         <v>1251.096525</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="AZ8" t="n">
         <v>180.443475</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
         <v>-1</v>
@@ -1878,132 +1905,135 @@
         <v>16815</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1618.2</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>397.396852</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>72.957</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>2666.8</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>4047.1</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>2193.1</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>374</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
       <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
         <v>173.4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>1899.924</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>175.3</v>
       </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
       <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>14.2</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>11</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>19.7</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>429.7</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>110.248</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>51.919</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>52.757</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>45</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
         <v>1473.053</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>182.147</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
         <v>-2201.688</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AK9" t="n">
         <v>-1220.328</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AL9" t="n">
         <v>-102.823333333333</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AM9" t="n">
         <v>-35.4366666666666</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
         <v>1691.3997</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AO9" t="n">
         <v>154.1025</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
         <v>114.6509</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AQ9" t="n">
         <v>69.393</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
         <v>272.843</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AS9" t="n">
         <v>44.17</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
         <v>209.427525</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>16.12079192</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>23.6231416</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AW9" t="n">
         <v>39.15</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AX9" t="n">
         <v>0.6759</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AY9" t="n">
         <v>1277.6076</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AZ9" t="n">
         <v>182.8674</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
         <v>-1</v>
@@ -2033,132 +2063,135 @@
         <v>17149</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1609</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>431.1872748</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>75.452</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>2727.2</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>4448.1</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2285.3</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>385</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
         <v>184.7</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>1930.924</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>177.2</v>
       </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>22.6</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>151</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>110.248</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>46.619</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>52.757</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>45</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>1514.338</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>201.462</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
         <v>-2296.824</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AK10" t="n">
         <v>-1253.778</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AL10" t="n">
         <v>-109.076666666667</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AM10" t="n">
         <v>-39.2</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AN10" t="n">
         <v>1687.3776</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AO10" t="n">
         <v>156.645</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AP10" t="n">
         <v>112.7448</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AQ10" t="n">
         <v>68.825</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
         <v>218.928</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
         <v>36.383</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
         <v>205.863525</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>14.371564</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>31.8029516</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>40.95</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
         <v>0.6534</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AY10" t="n">
         <v>1311.631875</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AZ10" t="n">
         <v>182.053125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" t="n">
         <v>-1</v>
@@ -2188,132 +2221,135 @@
         <v>17606.6</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1622.6</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>501.700032</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>2816.7</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>4479.1</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>2353.3</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>425.6</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>164.4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>1936.024</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>184.4</v>
       </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>20.8</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>129.4</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>110.248</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>39.719</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>52.757</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>45</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>1528.079</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>224.221</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
         <v>-2403.36</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AK11" t="n">
         <v>-1296.738</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AL11" t="n">
         <v>-116.41</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AM11" t="n">
         <v>-42.12</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AN11" t="n">
         <v>1729.372914</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>160.065</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AP11" t="n">
         <v>52.3712</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AQ11" t="n">
         <v>68.825</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AR11" t="n">
         <v>134.724</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AS11" t="n">
         <v>26.086</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AT11" t="n">
         <v>196.425675</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>16.24578</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>37.7590996</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>40.95</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
         <v>0.621225</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AY11" t="n">
         <v>1339.509375</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="AZ11" t="n">
         <v>182.953125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" t="n">
         <v>-1</v>
@@ -2343,132 +2379,135 @@
         <v>17893.1</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1639.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>483.564868</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>2847.4</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>4538.9</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>2270.7</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>416.9</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>4.73961878202226</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>169.6</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>1928.124</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>204.1</v>
       </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>22.7</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>118.4</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>110.248</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>27.819</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>52.757</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>45</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
         <v>1557.76</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
         <v>206.14</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
         <v>-2481.99</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AK12" t="n">
         <v>-1316.634</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AL12" t="n">
         <v>-123.41</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AM12" t="n">
         <v>-45.3033333333333</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AN12" t="n">
         <v>1731.3741</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AO12" t="n">
         <v>166.725</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AP12" t="n">
         <v>51.4976</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AQ12" t="n">
         <v>68.115</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AR12" t="n">
         <v>76.057</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AS12" t="n">
         <v>23.248</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
         <v>187.184025</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>18.119996</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>41.6178064</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>40.95</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>0.6246</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AY12" t="n">
         <v>1366.47675</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AZ12" t="n">
         <v>183.14325</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n">
         <v>-1</v>
@@ -2498,132 +2537,135 @@
         <v>18111.4</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1691.3</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>447.724928</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>76.0151428571429</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>2879.2</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>4511</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>2266.1</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>419.3</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>7.97769868483218</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>178.8</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>2003.084</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>257</v>
       </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.3</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>25.5</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>110.5</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>12.726</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>6.316</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>30</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
         <v>45</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AG13" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
         <v>1574.766</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>220.334</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
         <v>-2545.866</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AK13" t="n">
         <v>-1329.654</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AL13" t="n">
         <v>-129.656666666667</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AM13" t="n">
         <v>-48.92</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AN13" t="n">
         <v>1754.5851</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AO13" t="n">
         <v>185.1075</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AP13" t="n">
         <v>51.2176</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AQ13" t="n">
         <v>68.115</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AR13" t="n">
         <v>52.018</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
         <v>22.562</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
         <v>183.625425</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>16.093332</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>40.01589</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>40.95</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>0.627975</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AY13" t="n">
         <v>1389.362175</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AZ13" t="n">
         <v>191.735325</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" t="n">
         <v>-1</v>
@@ -2653,41 +2695,41 @@
         <v>18487</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1727.7</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>441.5435432</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>76.0151428571429</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>2912.8</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>4191.5</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2245.5</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>419.2</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>30.340947133778</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>173.9</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>2018.784</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>191.2</v>
       </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
@@ -2695,90 +2737,93 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>30</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>103.4</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>12.726</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>1.416</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
         <v>12</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AF14" t="n">
         <v>45</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AG14" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AH14" t="n">
         <v>1626.831</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AI14" t="n">
         <v>243.069</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AJ14" t="n">
         <v>-2558.034</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AK14" t="n">
         <v>-1342.134</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AL14" t="n">
         <v>-137.213333333333</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AM14" t="n">
         <v>-52.5999999999999</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AN14" t="n">
         <v>1774.3536</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AO14" t="n">
         <v>188.2575</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AP14" t="n">
         <v>18.424</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AQ14" t="n">
         <v>68.115</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AR14" t="n">
         <v>27.457</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AS14" t="n">
         <v>21.292</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AT14" t="n">
         <v>181.097775</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>14.066668</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
         <v>34.8458316</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AW14" t="n">
         <v>40.95</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AX14" t="n">
         <v>0.618525</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AY14" t="n">
         <v>1414.6731</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="AZ14" t="n">
         <v>201.0969</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" t="n">
         <v>-1</v>
@@ -2808,41 +2853,41 @@
         <v>18693.1</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1738.8</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>436.07272</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>76.0151428571429</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>2934.6</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>4210.6</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>2236.1</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>415.5</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>46.2453234375524</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>170.2</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>2006.42685714286</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>183.8</v>
       </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
@@ -2850,90 +2895,93 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>32.8</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>101.3</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>12.726</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>1.416</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>12</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AF15" t="n">
         <v>45</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AG15" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AH15" t="n">
         <v>1659.996</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AI15" t="n">
         <v>267.104</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AJ15" t="n">
         <v>-2564.838</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AK15" t="n">
         <v>-1347.348</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AL15" t="n">
         <v>-144.406666666667</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AM15" t="n">
         <v>-55.9899999999999</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AN15" t="n">
         <v>1790.19424285714</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AO15" t="n">
         <v>188.1225</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AP15" t="n">
         <v>2.1784</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AQ15" t="n">
         <v>41.153</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AR15" t="n">
         <v>9.157</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AS15" t="n">
         <v>22.948</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AT15" t="n">
         <v>159.5619</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>14.28301</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
         <v>28.9760264</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AW15" t="n">
         <v>40.95</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
         <v>0.5679</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AY15" t="n">
         <v>1444.354425</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="AZ15" t="n">
         <v>210.745575</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16" t="n">
         <v>-1</v>
@@ -2963,41 +3011,41 @@
         <v>18961.8</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1784.4</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>417.915944</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>76.0151428571429</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>3005.4</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>4257.9</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>2270.3</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>428.4</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>62.0712654345618</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>168.5</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>2016.42685714286</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>185.9</v>
       </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
@@ -3005,90 +3053,93 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>34.9</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>103.5</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>12.726</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>1.416</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
         <v>12</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AF16" t="n">
         <v>2.081508</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AG16" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AH16" t="n">
         <v>1613.65</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AI16" t="n">
         <v>290.05</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AJ16" t="n">
         <v>-2589.162</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AK16" t="n">
         <v>-1357.608</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AL16" t="n">
         <v>-150.096666666666</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AM16" t="n">
         <v>-58.8866666666666</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AN16" t="n">
         <v>1810.06238571429</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AO16" t="n">
         <v>184.0275</v>
       </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
       <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>41.153</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AR16" t="n">
         <v>0.67</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AS16" t="n">
         <v>26.182</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AT16" t="n">
         <v>136.667025</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>14.499352</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AV16" t="n">
         <v>22.99411</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AW16" t="n">
         <v>32.3663016</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AX16" t="n">
         <v>0.5706</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="AY16" t="n">
         <v>1456.929675</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="AZ16" t="n">
         <v>229.625325</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" t="n">
         <v>-1</v>
@@ -3118,41 +3169,41 @@
         <v>19190.6</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1812</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>434.045944</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>77.6741428571429</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>3049</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>4302.2</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>2301.1</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>442.7</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>68.3121900998493</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>172.7</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>2024.999</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>189.5</v>
       </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
@@ -3160,90 +3211,93 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>35.5</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>98</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>1.365</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>1.479</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
         <v>4.222</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AF17" t="n">
         <v>2.100618</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
         <v>1658.388</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AI17" t="n">
         <v>252.912</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AJ17" t="n">
         <v>-2609.964</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AK17" t="n">
         <v>-1367.988</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AL17" t="n">
         <v>-156.486666666666</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AM17" t="n">
         <v>-62.0366666666666</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AN17" t="n">
         <v>1814.99326071429</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AO17" t="n">
         <v>168.84</v>
       </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
       <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>41.153</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AR17" t="n">
         <v>0.174</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AS17" t="n">
         <v>28.155</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AT17" t="n">
         <v>126.927</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AU17" t="n">
         <v>14.261254</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
         <v>16.69038</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AW17" t="n">
         <v>25.07397996</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AX17" t="n">
         <v>0.5733</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AY17" t="n">
         <v>1475.744625</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="AZ17" t="n">
         <v>236.955375</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" t="n">
         <v>-1</v>
@@ -3273,41 +3327,41 @@
         <v>19443.8</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1834.3</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>361.852944</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>77.6741428571429</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>3097.5</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>4390.9</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>2325.5</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>472.3</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>78.0145380046553</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>173.2</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>2131.899</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>194.8</v>
       </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
@@ -3315,90 +3369,93 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>35.5</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>95</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>1.365</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>1.479</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
         <v>4.222</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AF18" t="n">
         <v>2.58153</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AG18" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AH18" t="n">
         <v>1680.381</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AI18" t="n">
         <v>298.119</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AJ18" t="n">
         <v>-2614.512</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AK18" t="n">
         <v>-1373.712</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AL18" t="n">
         <v>-162.896666666666</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AM18" t="n">
         <v>-65.0899999999999</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AN18" t="n">
         <v>1840.44413571429</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AO18" t="n">
         <v>169.65</v>
       </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
       <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>34.1285</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AR18" t="n">
         <v>0.08</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AS18" t="n">
         <v>29.581</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AT18" t="n">
         <v>118.68525</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AU18" t="n">
         <v>14.023156</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
         <v>12.61027</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AW18" t="n">
         <v>18.30645234</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AX18" t="n">
         <v>0.5418</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AY18" t="n">
         <v>1487.793375</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="AZ18" t="n">
         <v>249.341625</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" t="n">
         <v>-1</v>
@@ -3428,41 +3485,41 @@
         <v>19756.1</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1867.5</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>371.076109</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>77.6741428571429</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>3127.6</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>4456.6</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>2363.6</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>495.3</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>85.4387215838714</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>170.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>2160.999</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>199.2</v>
       </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
@@ -3470,90 +3527,93 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>36.1</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>93</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>1.365</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>1.479</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
         <v>4.222</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
         <v>2.604045</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AG19" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AH19" t="n">
         <v>1707.978</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AI19" t="n">
         <v>314.922</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AJ19" t="n">
         <v>-2622.426</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AK19" t="n">
         <v>-1378.08</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AL19" t="n">
         <v>-168.096666666666</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AM19" t="n">
         <v>-67.4566666666666</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AN19" t="n">
         <v>1875.22286785714</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AO19" t="n">
         <v>173.115</v>
       </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
       <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>27.388</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AR19" t="n">
         <v>0.035</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AS19" t="n">
         <v>30.805</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AT19" t="n">
         <v>96.491025</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AU19" t="n">
         <v>13.04705068</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AV19" t="n">
         <v>9.32794</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AW19" t="n">
         <v>11.95799418</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AX19" t="n">
         <v>0.4005</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AY19" t="n">
         <v>1498.589325</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="AZ19" t="n">
         <v>260.100675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" t="n">
         <v>-1</v>
@@ -3583,41 +3643,41 @@
         <v>20032.8</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1917.9</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>392.80533</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>77.6741428571429</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>3169.1</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4526.7</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>2400.1</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>490.6</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>79.7528365289157</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>170.1</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>2181.299</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>209</v>
       </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
@@ -3625,90 +3685,93 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>37</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
         <v>92.1</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>1.365</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>1.479</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AE20" t="n">
         <v>4.222</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AF20" t="n">
         <v>2.8036115</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AG20" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AH20" t="n">
         <v>1744.359</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AI20" t="n">
         <v>315.441</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AJ20" t="n">
         <v>-2629.842</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AK20" t="n">
         <v>-1390.32</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AL20" t="n">
         <v>-172.826666666666</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AM20" t="n">
         <v>-69.0033333333332</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AN20" t="n">
         <v>1912.3191</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AO20" t="n">
         <v>178.3125</v>
       </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
       <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>20.6475</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AR20" t="n">
         <v>0.012</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AS20" t="n">
         <v>31.843</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AT20" t="n">
         <v>75.838725</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AU20" t="n">
         <v>8.517842</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AV20" t="n">
         <v>6.35096</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AW20" t="n">
         <v>8.21888317</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AX20" t="n">
         <v>0.4014</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="AY20" t="n">
         <v>1527.99885</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="AZ20" t="n">
         <v>265.81365</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" t="n">
         <v>-1</v>
@@ -3738,41 +3801,41 @@
         <v>20351.3</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1950</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>397.5193257</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>79.2681428571429</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>3200.8</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4590.3</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>2436.6</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>508.6</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>71.3023025089479</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>174.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>2212.098</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>204.3</v>
       </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
@@ -3780,90 +3843,93 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
         <v>37.3</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AB21" t="n">
         <v>94</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>-0.901</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>1.63</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AE21" t="n">
         <v>2.372</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AF21" t="n">
         <v>2.833394</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AG21" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AH21" t="n">
         <v>1786.697</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AI21" t="n">
         <v>314.303</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AJ21" t="n">
         <v>-2642.622</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AK21" t="n">
         <v>-1404.93</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AL21" t="n">
         <v>-177.313333333333</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AM21" t="n">
         <v>-69.0299999999999</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AN21" t="n">
         <v>1954.416375</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AO21" t="n">
         <v>181.6425</v>
       </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
       <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>13.836</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
       <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>32.631</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AT21" t="n">
         <v>65.877975</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AU21" t="n">
         <v>6.576191</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
         <v>4.56094</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AW21" t="n">
         <v>6.190300475</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AX21" t="n">
         <v>0.4023</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AY21" t="n">
         <v>1556.868375</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="AZ21" t="n">
         <v>279.626625</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" t="n">
         <v>-1</v>
@@ -3893,41 +3959,41 @@
         <v>20555</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1949.7</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>402.652997</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>79.2681428571429</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>3245.8</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>4710.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>2460.1</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>469.2</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>64.0053588682794</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>184.4</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2312.798</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>203.3</v>
       </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
@@ -3935,90 +4001,93 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
         <v>37.1</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>107</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>-0.901</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>1.63</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AE22" t="n">
         <v>2.372</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AF22" t="n">
         <v>2.8239574</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AG22" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AH22" t="n">
         <v>1811.332</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AI22" t="n">
         <v>316.468</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AJ22" t="n">
         <v>-2684.838</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AK22" t="n">
         <v>-1421.406</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AL22" t="n">
         <v>-180.12</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AM22" t="n">
         <v>-69.0199999999999</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AN22" t="n">
         <v>1995.11865</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AO22" t="n">
         <v>183.555</v>
       </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
       <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>7.0245</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
       <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
         <v>33.123</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AT22" t="n">
         <v>61.47135</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AU22" t="n">
         <v>4.63454</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AV22" t="n">
         <v>3.85754</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AW22" t="n">
         <v>4.12709705</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AX22" t="n">
         <v>0.3861</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="AY22" t="n">
         <v>1586.33235</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="AZ22" t="n">
         <v>283.75515</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23" t="n">
         <v>-1</v>
@@ -4048,41 +4117,41 @@
         <v>20789.9</v>
       </c>
       <c r="L23" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M23" t="n">
         <v>1956.4</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>378.8256195</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>3280.6</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>4925.4</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>2490.5</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>469.7</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>80.4735419865758</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>183</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>2409.698</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>203.5</v>
       </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
@@ -4090,90 +4159,93 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
         <v>38</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>119.2</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>-0.901</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>1.63</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AE23" t="n">
         <v>2.372</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AF23" t="n">
         <v>2.8656558</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AG23" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AH23" t="n">
         <v>1877.66</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AI23" t="n">
         <v>319.14</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AJ23" t="n">
         <v>-2747.832</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AK23" t="n">
         <v>-1439.904</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AL23" t="n">
         <v>-181.59</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AM23" t="n">
         <v>-69.6399999999999</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AN23" t="n">
         <v>2051.075925</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AO23" t="n">
         <v>184.5225</v>
       </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
       <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>0.213</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
       <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
         <v>33.62</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AT23" t="n">
         <v>55.2555</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AU23" t="n">
         <v>2.745007</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
         <v>3.17264</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AW23" t="n">
         <v>2.478820453</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AX23" t="n">
         <v>0.315</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AY23" t="n">
         <v>1624.5108</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="AZ23" t="n">
         <v>284.7042</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C24" t="n">
         <v>-1</v>
@@ -4203,41 +4275,41 @@
         <v>21111.2</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1989.7</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>310.806928</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>3334.7</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>5072.3</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>2523.6</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>208.5</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>98.524631049651</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>166.7</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>2371.898</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>204</v>
       </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
@@ -4245,90 +4317,93 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
         <v>38.5</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
         <v>123.4</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>-0.901</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>1.63</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AE24" t="n">
         <v>2.372</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AF24" t="n">
         <v>-8.076788</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AG24" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AH24" t="n">
         <v>1936.933</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AI24" t="n">
         <v>346.267</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AJ24" t="n">
         <v>-2818.38</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AK24" t="n">
         <v>-1458.912</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AL24" t="n">
         <v>-174.643333333333</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AM24" t="n">
         <v>-69.5433333333333</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AN24" t="n">
         <v>2093.9607</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AO24" t="n">
         <v>183.3975</v>
       </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
       <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>0.142</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
       <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
         <v>34.021</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AT24" t="n">
         <v>50.655375</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AU24" t="n">
         <v>0.855474</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AV24" t="n">
         <v>2.58402</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AW24" t="n">
         <v>0.344274675</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AX24" t="n">
         <v>0.315</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AY24" t="n">
         <v>1667.83995</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="AZ24" t="n">
         <v>291.64005</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C25" t="n">
         <v>-1</v>
@@ -4358,41 +4433,41 @@
         <v>21363.4</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1971.8</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>291.1033188</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>3371.7</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>5141.9</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>2568.6</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>457.716813873374</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>110.469375919111</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>186.3</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>2375.939</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>205.6</v>
       </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
@@ -4400,90 +4475,93 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
         <v>38.3</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
         <v>95.9</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>-2.15</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>1.671</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AE25" t="n">
         <v>0.49</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AF25" t="n">
         <v>-8.046285</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AG25" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AH25" t="n">
         <v>1975.026</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AI25" t="n">
         <v>344.974</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AJ25" t="n">
         <v>-2881.752</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AK25" t="n">
         <v>-1479.648</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AL25" t="n">
         <v>-175.923893795779</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AM25" t="n">
         <v>-69.7933333333333</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AN25" t="n">
         <v>2130.824925</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AO25" t="n">
         <v>183.69</v>
       </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
       <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>0.071</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
       <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
         <v>34.282</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AT25" t="n">
         <v>47.119725</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AU25" t="n">
         <v>0.573855</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AV25" t="n">
         <v>2.04112</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AW25" t="n">
         <v>-1.471562937</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AX25" t="n">
         <v>0.315</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AY25" t="n">
         <v>1710.213975</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="AZ25" t="n">
         <v>298.541025</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C26" t="n">
         <v>-1</v>
@@ -4513,41 +4591,41 @@
         <v>21634.9</v>
       </c>
       <c r="L26" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M26" t="n">
         <v>1986.8</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>299.279</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>3429.9</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>5068.9</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>2595</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>589.6</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>135.971828422603</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>194.4</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>2392.3</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>204</v>
       </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
@@ -4555,14 +4633,14 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>36.4</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>133.9</v>
       </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
@@ -4573,35 +4651,35 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AH26" t="n">
         <v>2012.824</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
         <v>348.376</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AJ26" t="n">
         <v>-2922.228</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AK26" t="n">
         <v>-1500.102</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AL26" t="n">
         <v>-181.603893795779</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AM26" t="n">
         <v>-70.4766666666666</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AN26" t="n">
         <v>2148.712875</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AO26" t="n">
         <v>183.8475</v>
       </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
       <c r="AP26" t="n">
         <v>0</v>
       </c>
@@ -4609,36 +4687,39 @@
         <v>0</v>
       </c>
       <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
         <v>34.149</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AT26" t="n">
         <v>48.21165</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
         <v>0.378236</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AV26" t="n">
         <v>1.53068</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AW26" t="n">
         <v>-1.590137919</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="AX26" t="n">
         <v>0.315</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="AY26" t="n">
         <v>1755.549675</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="AZ26" t="n">
         <v>305.720325</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C27" t="n">
         <v>-1</v>
@@ -4668,41 +4749,41 @@
         <v>22078.2</v>
       </c>
       <c r="L27" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M27" t="n">
         <v>1988.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>299.298764494522</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>3557.7</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>5077.9</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>2661.5</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>241.246203643845</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>156.945251003532</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>195.003186671885</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>2427.12533142837</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>204.5</v>
       </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
@@ -4710,14 +4791,14 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>35.4</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
         <v>127.6</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
       <c r="AC27" t="n">
         <v>0</v>
       </c>
@@ -4728,35 +4809,35 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AH27" t="n">
         <v>2073.594</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AI27" t="n">
         <v>334.506</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AJ27" t="n">
         <v>-2955.666</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AK27" t="n">
         <v>-1523.55</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AL27" t="n">
         <v>-175.79543391724</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AM27" t="n">
         <v>-71.3034395557294</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AN27" t="n">
         <v>2152.63402457138</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AO27" t="n">
         <v>184.0725</v>
       </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
       <c r="AP27" t="n">
         <v>0</v>
       </c>
@@ -4764,36 +4845,39 @@
         <v>0</v>
       </c>
       <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
         <v>33.791</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AT27" t="n">
         <v>48.97845</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
         <v>0.211344</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AV27" t="n">
         <v>1.05376</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AW27" t="n">
         <v>-1.846002748</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AX27" t="n">
         <v>0.315</v>
       </c>
-      <c r="AX27" t="n">
+      <c r="AY27" t="n">
         <v>1799.634825</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="AZ27" t="n">
         <v>309.177675</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -4823,41 +4907,41 @@
         <v>22328.3302822231</v>
       </c>
       <c r="L28" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M28" t="n">
         <v>1990.94985569376</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>303.149342835201</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>3592.11619795648</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>5141.88107274062</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>2691.7125673033</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>234.554732670156</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>164.885835526837</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>195.725923855314</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>2428.70399810338</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>205.01125</v>
       </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
@@ -4865,14 +4949,14 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>35.7</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
         <v>127.6</v>
       </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
       <c r="AC28" t="n">
         <v>0</v>
       </c>
@@ -4886,32 +4970,32 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
         <v>2099.18751513857</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AI28" t="n">
         <v>353.888528819878</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AJ28" t="n">
         <v>-2996.95572872887</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AK28" t="n">
         <v>-1546.8495080764</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AL28" t="n">
         <v>-169.333925006246</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AM28" t="n">
         <v>-72.2109703509065</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AN28" t="n">
         <v>2165.41537414464</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AO28" t="n">
         <v>184.30003125</v>
       </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
       <c r="AP28" t="n">
         <v>0</v>
       </c>
@@ -4919,36 +5003,39 @@
         <v>0</v>
       </c>
       <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
         <v>33.439</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AT28" t="n">
         <v>49.810725</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="AU28" t="n">
         <v>-0.00499800000000003</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
         <v>0.61906</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AW28" t="n">
         <v>-1.53603725</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="AX28" t="n">
         <v>0.28035</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="AY28" t="n">
         <v>1836.14209090618</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="AZ28" t="n">
         <v>310.892518984473</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s">
         <v>80</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -4978,41 +5065,41 @@
         <v>22563.9793375807</v>
       </c>
       <c r="L29" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M29" t="n">
         <v>2003.26853546139</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>305.028009083171</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>3623.82533593147</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>5175.90684628522</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>2720.09035532397</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>598.747390352136</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>162.643016309613</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>196.954033655728</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>2448.24958231966</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>205.523778125</v>
       </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
@@ -5020,14 +5107,14 @@
         <v>0</v>
       </c>
       <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
         <v>35.7</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
         <v>127.6</v>
       </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
@@ -5041,32 +5128,32 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
         <v>2118.23637777865</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AI29" t="n">
         <v>355.495583527084</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AJ29" t="n">
         <v>-3037.9725502831</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AK29" t="n">
         <v>-1567.37435071527</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AL29" t="n">
         <v>-174.53550468465</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AM29" t="n">
         <v>-73.0194381394308</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AN29" t="n">
         <v>2181.68525516657</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AO29" t="n">
         <v>184.282881328125</v>
       </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
       <c r="AP29" t="n">
         <v>0</v>
       </c>
@@ -5074,36 +5161,39 @@
         <v>0</v>
       </c>
       <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
         <v>33.089</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AT29" t="n">
         <v>50.8527</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AU29" t="n">
         <v>-0.028203</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AV29" t="n">
         <v>0.37618</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AW29" t="n">
         <v>-0.871763964</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AX29" t="n">
         <v>0.250425</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AY29" t="n">
         <v>1868.36442590637</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="AZ29" t="n">
         <v>313.259875278067</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -5133,41 +5223,41 @@
         <v>22782.5142157335</v>
       </c>
       <c r="L30" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M30" t="n">
         <v>2014.4972488631</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>307.93504</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>3656.93449416565</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>5383.59003277666</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>2745.98970637937</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>604.344583169676</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>143.140105616203</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>196.350846983843</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>2501.79132865709</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>206.037587570312</v>
       </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
@@ -5175,14 +5265,14 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
         <v>36.7</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>127.6</v>
       </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
@@ -5196,32 +5286,32 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
         <v>2144.55517470178</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AI30" t="n">
         <v>355.19018729341</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AJ30" t="n">
         <v>-3092.83648985186</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AK30" t="n">
         <v>-1587.7843614426</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AL30" t="n">
         <v>-178.936990790306</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AM30" t="n">
         <v>-73.7911330388922</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AN30" t="n">
         <v>2206.32080411441</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AO30" t="n">
         <v>184.741338531445</v>
       </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
       <c r="AP30" t="n">
         <v>0</v>
       </c>
@@ -5229,36 +5319,39 @@
         <v>0</v>
       </c>
       <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
         <v>33.067</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AT30" t="n">
         <v>51.768</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AU30" t="n">
         <v>-0.051408</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AV30" t="n">
         <v>0.23798</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AW30" t="n">
         <v>-0.691527418</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AX30" t="n">
         <v>0.222075</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="AY30" t="n">
         <v>1898.00394021428</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="AZ30" t="n">
         <v>314.793067419084</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -5288,41 +5381,41 @@
         <v>22992.8464409065</v>
       </c>
       <c r="L31" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M31" t="n">
         <v>2024.92165780942</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>310.870715074303</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3689.96355630547</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>5418.83660930042</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2771.93863237722</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>609.994099501175</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>115.322937925207</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>196.443226924582</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2516.94052676424</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>206.552681539238</v>
       </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
@@ -5330,14 +5423,14 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
         <v>37.7</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>127.6</v>
       </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
       <c r="AC31" t="n">
         <v>0</v>
       </c>
@@ -5351,32 +5444,32 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
         <v>2171.66261222546</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AI31" t="n">
         <v>354.497037426154</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
         <v>-3137.0184721908</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AK31" t="n">
         <v>-1607.78157600843</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AL31" t="n">
         <v>-182.760127440345</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AM31" t="n">
         <v>-74.6525739363783</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AN31" t="n">
         <v>2226.52922306498</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AO31" t="n">
         <v>185.203191877774</v>
       </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
       <c r="AP31" t="n">
         <v>0</v>
       </c>
@@ -5384,36 +5477,39 @@
         <v>0</v>
       </c>
       <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
         <v>33.307</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AT31" t="n">
         <v>52.6842</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AU31" t="n">
         <v>-0.074613</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AV31" t="n">
         <v>0.11938</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AW31" t="n">
         <v>-0.72538577</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AX31" t="n">
         <v>0.1953</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AY31" t="n">
         <v>1920.069377965</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="AZ31" t="n">
         <v>319.291050839969</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -5443,41 +5539,41 @@
         <v>23214.621873323</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>2035.9182023489</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>313.835316548609</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>3721.81743724505</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>5454.35505149539</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>2798.95682914633</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>615.696428475773</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>85.0823596752584</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>196.19325767317</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>2532.34336351648</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>207.069063243086</v>
       </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
@@ -5485,14 +5581,14 @@
         <v>0</v>
       </c>
       <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
         <v>38.7</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
         <v>127.6</v>
       </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
@@ -5506,32 +5602,32 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
         <v>2195.564390209</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AI32" t="n">
         <v>358.416834279241</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AJ32" t="n">
         <v>-3164.18767640365</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AK32" t="n">
         <v>-1627.48101312322</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AL32" t="n">
         <v>-186.930008389538</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AM32" t="n">
         <v>-75.5223491921506</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AN32" t="n">
         <v>2249.84808028293</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AO32" t="n">
         <v>185.666199857468</v>
       </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
       <c r="AP32" t="n">
         <v>0</v>
       </c>
@@ -5539,36 +5635,39 @@
         <v>0</v>
       </c>
       <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
         <v>33.711</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AT32" t="n">
         <v>53.56845</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AU32" t="n">
         <v>-0.097818</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AV32" t="n">
         <v>0.0196</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AW32" t="n">
         <v>-0.3218514</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AX32" t="n">
         <v>0.171675</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AY32" t="n">
         <v>1941.75417485585</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="AZ32" t="n">
         <v>320.309919568325</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -5598,41 +5697,41 @@
         <v>23434.3719593246</v>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>2041.65555292291</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>316.829129446497</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>3753.53818707383</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>5489.39569550016</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>2826.31248358626</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>620.498876538429</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>50.6890505411461</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>197.557220327612</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>2549.71011858832</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>207.586735901194</v>
       </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
@@ -5640,14 +5739,14 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
         <v>39.7</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
         <v>127.6</v>
       </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
       <c r="AC33" t="n">
         <v>0</v>
       </c>
@@ -5661,32 +5760,32 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
         <v>2232.55499411875</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AI33" t="n">
         <v>365.436265662356</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AJ33" t="n">
         <v>-3189.27096330564</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AK33" t="n">
         <v>-1646.20619321094</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AL33" t="n">
         <v>-190.659970940819</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AM33" t="n">
         <v>-76.300923203071</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AN33" t="n">
         <v>2272.67670094338</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AO33" t="n">
         <v>186.130365357112</v>
       </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
       <c r="AP33" t="n">
         <v>0</v>
       </c>
@@ -5694,36 +5793,39 @@
         <v>0</v>
       </c>
       <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
         <v>34.28</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AT33" t="n">
         <v>54.653625</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AU33" t="n">
         <v>-0.082501</v>
       </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
       <c r="AV33" t="n">
         <v>0</v>
       </c>
       <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
         <v>0.14805</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AY33" t="n">
         <v>1967.47586353237</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="AZ33" t="n">
         <v>322.546573048761</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -5753,41 +5855,41 @@
         <v>23661.6158270609</v>
       </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>2045.40187508747</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>319.8524416</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3785.12671651503</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>5572.3334479222</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>2854.3057827196</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>625.338783820155</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>28.4306176015575</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>197.242041706267</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>2568.16679225807</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>208.105702740947</v>
       </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
@@ -5795,14 +5897,14 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
         <v>39.7</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AB34" t="n">
         <v>128.6</v>
       </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
       <c r="AC34" t="n">
         <v>0</v>
       </c>
@@ -5816,32 +5918,32 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
         <v>2268.93037486315</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AI34" t="n">
         <v>373.867091412813</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AJ34" t="n">
         <v>-3226.55567396658</v>
       </c>
-      <c r="AJ34" t="n">
+      <c r="AK34" t="n">
         <v>-1665.08547738852</v>
       </c>
-      <c r="AK34" t="n">
+      <c r="AL34" t="n">
         <v>-195.864597068157</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AM34" t="n">
         <v>-76.7289912599466</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AN34" t="n">
         <v>2287.6111802536</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AO34" t="n">
         <v>186.595691270505</v>
       </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
       <c r="AP34" t="n">
         <v>0</v>
       </c>
@@ -5849,36 +5951,39 @@
         <v>0</v>
       </c>
       <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
         <v>34.825</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AT34" t="n">
         <v>55.3248</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AU34" t="n">
         <v>-0.067184</v>
       </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
       <c r="AV34" t="n">
         <v>0</v>
       </c>
       <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
         <v>0.124425</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AY34" t="n">
         <v>1995.46028356868</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="AZ34" t="n">
         <v>326.748876475627</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -5908,41 +6013,41 @@
         <v>23882.8849228737</v>
       </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>2053.28720486566</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>312.905543677275</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>75.1961428571429</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>3817.00876784</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>5609.46393518282</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>2882.00396607354</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>630.216442503827</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>10.8884618270169</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>197.089886509756</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>2587.71443212373</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>208.625966997799</v>
       </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
@@ -5950,14 +6055,14 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
         <v>39.7</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AB35" t="n">
         <v>128.6</v>
       </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
       <c r="AC35" t="n">
         <v>0</v>
       </c>
@@ -5971,32 +6076,32 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
         <v>2306.28413399849</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AI35" t="n">
         <v>382.130773934261</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AJ35" t="n">
         <v>-3265.65360445851</v>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AK35" t="n">
         <v>-1681.65720430216</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AL35" t="n">
         <v>-201.215145151618</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AM35" t="n">
         <v>-77.1986541436051</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AN35" t="n">
         <v>2303.53530895948</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AO35" t="n">
         <v>187.062180498681</v>
       </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
       <c r="AP35" t="n">
         <v>0</v>
       </c>
@@ -6004,27 +6109,30 @@
         <v>0</v>
       </c>
       <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
         <v>35.287</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AT35" t="n">
         <v>55.83015</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
         <v>-0.051867</v>
       </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
       <c r="AV35" t="n">
         <v>0</v>
       </c>
       <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
         <v>0.1008</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="AY35" t="n">
         <v>2025.75012596761</v>
       </c>
-      <c r="AY35" t="n">
+      <c r="AZ35" t="n">
         <v>332.966467189951</v>
       </c>
     </row>
@@ -6074,132 +6182,132 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AG1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AI1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AJ1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AK1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AL1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AM1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AN1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AO1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AP1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AQ1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AR1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AS1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AT1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AU1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AV1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AW1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AX1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AY1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -6351,10 +6459,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -6506,10 +6614,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
         <v>-1</v>
@@ -6661,10 +6769,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
         <v>-1</v>
@@ -6816,10 +6924,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
         <v>-1</v>
@@ -6971,10 +7079,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
         <v>-1</v>
@@ -7126,10 +7234,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
         <v>-1</v>
@@ -7281,10 +7389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
         <v>-1</v>
@@ -7436,10 +7544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
         <v>-1</v>
@@ -7591,10 +7699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" t="n">
         <v>-1</v>
@@ -7746,10 +7854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" t="n">
         <v>-1</v>
@@ -7901,10 +8009,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n">
         <v>-1</v>
@@ -8056,10 +8164,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" t="n">
         <v>-1</v>
@@ -8211,10 +8319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" t="n">
         <v>-1</v>
@@ -8366,10 +8474,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16" t="n">
         <v>-1</v>
@@ -8521,10 +8629,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" t="n">
         <v>-1</v>
@@ -8676,10 +8784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" t="n">
         <v>-1</v>
@@ -8831,10 +8939,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" t="n">
         <v>-1</v>
@@ -8986,10 +9094,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" t="n">
         <v>-1</v>
@@ -9141,10 +9249,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" t="n">
         <v>-1</v>
@@ -9296,10 +9404,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" t="n">
         <v>-1</v>
@@ -9451,10 +9559,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23" t="n">
         <v>-1</v>
@@ -9606,10 +9714,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C24" t="n">
         <v>-1</v>
@@ -9761,10 +9869,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C25" t="n">
         <v>-1</v>
@@ -9916,10 +10024,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C26" t="n">
         <v>-1</v>
@@ -9967,7 +10075,7 @@
         <v>2595</v>
       </c>
       <c r="R26" t="n">
-        <v>445.021075130373</v>
+        <v>589.6</v>
       </c>
       <c r="S26" t="n">
         <v>135.971828422603</v>
@@ -10024,7 +10132,7 @@
         <v>-1500.102</v>
       </c>
       <c r="AK26" t="n">
-        <v>-176.784596300125</v>
+        <v>-181.603893795779</v>
       </c>
       <c r="AL26" t="n">
         <v>-70.4766666666666</v>
@@ -10071,40 +10179,40 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00782752737609238</v>
+        <v>0.0113144084148564</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00836928979415164</v>
+        <v>0.0379149011299436</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00836928979415164</v>
+        <v>0.0196168690910377</v>
       </c>
       <c r="G27" t="n">
-        <v>0.00836928979415164</v>
+        <v>0.034366320713346</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00687456037750667</v>
+        <v>0.0125795380047049</v>
       </c>
       <c r="I27" t="n">
         <v>0.00525368446989161</v>
       </c>
       <c r="J27" t="n">
-        <v>32242.0170972532</v>
+        <v>32475.2</v>
       </c>
       <c r="K27" t="n">
-        <v>21905.8863613565</v>
+        <v>22078.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1993.22590350582</v>
+        <v>1988.4</v>
       </c>
       <c r="M27" t="n">
         <v>299.298764494522</v>
@@ -10113,28 +10221,28 @@
         <v>75.1961428571429</v>
       </c>
       <c r="O27" t="n">
-        <v>3462.63828806306</v>
+        <v>3557.7</v>
       </c>
       <c r="P27" t="n">
-        <v>5034.82407316799</v>
+        <v>5077.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>2636.67277279961</v>
+        <v>2661.5</v>
       </c>
       <c r="R27" t="n">
-        <v>132.67747940975</v>
+        <v>241.246203643845</v>
       </c>
       <c r="S27" t="n">
         <v>156.945251003532</v>
       </c>
       <c r="T27" t="n">
-        <v>190.520753545182</v>
+        <v>195.003186671885</v>
       </c>
       <c r="U27" t="n">
-        <v>2397.94464746135</v>
+        <v>2427.12533142837</v>
       </c>
       <c r="V27" t="n">
-        <v>204.51</v>
+        <v>204.5</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -10146,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>35.7</v>
+        <v>35.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>133.9</v>
+        <v>127.6</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -10164,31 +10272,31 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>2035.51760712452</v>
+        <v>2073.594</v>
       </c>
       <c r="AH27" t="n">
-        <v>345.800981275389</v>
+        <v>334.506</v>
       </c>
       <c r="AI27" t="n">
-        <v>-2950.49688878016</v>
+        <v>-2955.666</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-1520.57073273595</v>
+        <v>-1523.55</v>
       </c>
       <c r="AK27" t="n">
-        <v>-167.357178947116</v>
+        <v>-175.79543391724</v>
       </c>
       <c r="AL27" t="n">
-        <v>-71.1540251181726</v>
+        <v>-71.3034395557294</v>
       </c>
       <c r="AM27" t="n">
-        <v>2146.0683706788</v>
+        <v>2152.63402457138</v>
       </c>
       <c r="AN27" t="n">
-        <v>184.07475</v>
+        <v>184.0725</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -10200,10 +10308,10 @@
         <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>33.851</v>
+        <v>33.791</v>
       </c>
       <c r="AS27" t="n">
-        <v>49.2903</v>
+        <v>48.97845</v>
       </c>
       <c r="AT27" t="n">
         <v>0.211344</v>
@@ -10215,21 +10323,21 @@
         <v>-1.846002748</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.28035</v>
+        <v>0.315</v>
       </c>
       <c r="AX27" t="n">
-        <v>1791.06763660302</v>
+        <v>1799.634825</v>
       </c>
       <c r="AY27" t="n">
-        <v>311.719045786963</v>
+        <v>309.177675</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -10253,13 +10361,13 @@
         <v>0.00537994009364007</v>
       </c>
       <c r="J28" t="n">
-        <v>32617.1286939279</v>
+        <v>32853.0245042047</v>
       </c>
       <c r="K28" t="n">
-        <v>22154.0644527731</v>
+        <v>22328.3302822231</v>
       </c>
       <c r="L28" t="n">
-        <v>1995.8134991428</v>
+        <v>1990.94985569376</v>
       </c>
       <c r="M28" t="n">
         <v>303.149342835201</v>
@@ -10268,28 +10376,28 @@
         <v>75.1961428571429</v>
       </c>
       <c r="O28" t="n">
-        <v>3496.13488552031</v>
+        <v>3592.11619795648</v>
       </c>
       <c r="P28" t="n">
-        <v>5072.3688445901</v>
+        <v>5141.88107274062</v>
       </c>
       <c r="Q28" t="n">
-        <v>2666.55786673422</v>
+        <v>2691.7125673033</v>
       </c>
       <c r="R28" t="n">
-        <v>128.997390401414</v>
+        <v>234.554732670156</v>
       </c>
       <c r="S28" t="n">
         <v>164.885835526837</v>
       </c>
       <c r="T28" t="n">
-        <v>191.189814718973</v>
+        <v>195.725923855314</v>
       </c>
       <c r="U28" t="n">
-        <v>2422.11263725899</v>
+        <v>2428.70399810338</v>
       </c>
       <c r="V28" t="n">
-        <v>205.021275</v>
+        <v>205.01125</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -10304,7 +10412,7 @@
         <v>35.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>133.9</v>
+        <v>127.6</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -10322,28 +10430,28 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2080.72182036767</v>
+        <v>2099.18751513857</v>
       </c>
       <c r="AH28" t="n">
-        <v>351.399497154</v>
+        <v>353.888528819878</v>
       </c>
       <c r="AI28" t="n">
-        <v>-2983.44515013097</v>
+        <v>-2996.95572872887</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-1540.85167674406</v>
+        <v>-1546.8495080764</v>
       </c>
       <c r="AK28" t="n">
-        <v>-157.377091960497</v>
+        <v>-169.333925006246</v>
       </c>
       <c r="AL28" t="n">
-        <v>-71.9103522754718</v>
+        <v>-72.2109703509065</v>
       </c>
       <c r="AM28" t="n">
-        <v>2157.36666406208</v>
+        <v>2165.41537414464</v>
       </c>
       <c r="AN28" t="n">
-        <v>184.304536875</v>
+        <v>184.30003125</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -10355,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>33.49</v>
+        <v>33.439</v>
       </c>
       <c r="AS28" t="n">
-        <v>50.3919</v>
+        <v>49.810725</v>
       </c>
       <c r="AT28" t="n">
         <v>-0.00499800000000003</v>
@@ -10370,21 +10478,21 @@
         <v>-1.53603725</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.250425</v>
+        <v>0.28035</v>
       </c>
       <c r="AX28" t="n">
-        <v>1823.42012118574</v>
+        <v>1836.14209090618</v>
       </c>
       <c r="AY28" t="n">
-        <v>312.873857646613</v>
+        <v>310.892518984473</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s">
         <v>80</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -10408,13 +10516,13 @@
         <v>0.00537181203616477</v>
       </c>
       <c r="J29" t="n">
-        <v>32963.7101102449</v>
+        <v>33202.1124901464</v>
       </c>
       <c r="K29" t="n">
-        <v>22387.8743388971</v>
+        <v>22563.9793375807</v>
       </c>
       <c r="L29" t="n">
-        <v>2008.16227191654</v>
+        <v>2003.26853546139</v>
       </c>
       <c r="M29" t="n">
         <v>305.028009083171</v>
@@ -10423,28 +10531,28 @@
         <v>75.1961428571429</v>
       </c>
       <c r="O29" t="n">
-        <v>3526.99675561438</v>
+        <v>3623.82533593147</v>
       </c>
       <c r="P29" t="n">
-        <v>5105.89539616312</v>
+        <v>5175.90684628522</v>
       </c>
       <c r="Q29" t="n">
-        <v>2694.62842095072</v>
+        <v>2720.09035532397</v>
       </c>
       <c r="R29" t="n">
-        <v>455.419376403618</v>
+        <v>598.747390352136</v>
       </c>
       <c r="S29" t="n">
         <v>162.643016309613</v>
       </c>
       <c r="T29" t="n">
-        <v>192.326715660905</v>
+        <v>196.954033655728</v>
       </c>
       <c r="U29" t="n">
-        <v>2441.3239889774</v>
+        <v>2448.24958231966</v>
       </c>
       <c r="V29" t="n">
-        <v>205.5338281875</v>
+        <v>205.523778125</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -10459,7 +10567,7 @@
         <v>35.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>133.9</v>
+        <v>127.6</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -10477,28 +10585,28 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2098.91486020164</v>
+        <v>2118.23637777865</v>
       </c>
       <c r="AH29" t="n">
-        <v>354.271506931401</v>
+        <v>355.495583527084</v>
       </c>
       <c r="AI29" t="n">
-        <v>-3018.64515328046</v>
+        <v>-3037.9725502831</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-1559.81072089017</v>
+        <v>-1567.37435071527</v>
       </c>
       <c r="AK29" t="n">
-        <v>-157.801071173951</v>
+        <v>-174.53550468465</v>
       </c>
       <c r="AL29" t="n">
-        <v>-72.5645761308352</v>
+        <v>-73.0194381394308</v>
       </c>
       <c r="AM29" t="n">
-        <v>2172.07828658199</v>
+        <v>2181.68525516657</v>
       </c>
       <c r="AN29" t="n">
-        <v>184.289648217188</v>
+        <v>184.282881328125</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -10510,10 +10618,10 @@
         <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>33.137</v>
+        <v>33.089</v>
       </c>
       <c r="AS29" t="n">
-        <v>51.689025</v>
+        <v>50.8527</v>
       </c>
       <c r="AT29" t="n">
         <v>-0.028203</v>
@@ -10525,21 +10633,21 @@
         <v>-0.871763964</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.222075</v>
+        <v>0.250425</v>
       </c>
       <c r="AX29" t="n">
-        <v>1851.29511473111</v>
+        <v>1868.36442590637</v>
       </c>
       <c r="AY29" t="n">
-        <v>314.965796706178</v>
+        <v>313.259875278067</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -10563,13 +10671,13 @@
         <v>0.00535544010784861</v>
       </c>
       <c r="J30" t="n">
-        <v>33299.1406462108</v>
+        <v>33539.9689495839</v>
       </c>
       <c r="K30" t="n">
-        <v>22604.7036187663</v>
+        <v>22782.5142157335</v>
       </c>
       <c r="L30" t="n">
-        <v>2019.41841567176</v>
+        <v>2014.4972488631</v>
       </c>
       <c r="M30" t="n">
         <v>307.93504</v>
@@ -10578,28 +10686,28 @@
         <v>75.1961428571429</v>
       </c>
       <c r="O30" t="n">
-        <v>3559.22123743894</v>
+        <v>3656.93449416565</v>
       </c>
       <c r="P30" t="n">
-        <v>5343.18971939587</v>
+        <v>5383.59003277666</v>
       </c>
       <c r="Q30" t="n">
-        <v>2720.24861885097</v>
+        <v>2745.98970637937</v>
       </c>
       <c r="R30" t="n">
-        <v>459.676714479156</v>
+        <v>604.344583169676</v>
       </c>
       <c r="S30" t="n">
         <v>143.140105616203</v>
       </c>
       <c r="T30" t="n">
-        <v>191.768326260221</v>
+        <v>196.350846983843</v>
       </c>
       <c r="U30" t="n">
-        <v>2494.2235816974</v>
+        <v>2501.79132865709</v>
       </c>
       <c r="V30" t="n">
-        <v>206.047662757969</v>
+        <v>206.037587570312</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -10614,7 +10722,7 @@
         <v>36.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>133.9</v>
+        <v>127.6</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -10632,28 +10740,28 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2123.97914216726</v>
+        <v>2144.55517470178</v>
       </c>
       <c r="AH30" t="n">
-        <v>355.632237528028</v>
+        <v>355.19018729341</v>
       </c>
       <c r="AI30" t="n">
-        <v>-3072.83178893256</v>
+        <v>-3092.83648985186</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-1578.64108314823</v>
+        <v>-1587.7843614426</v>
       </c>
       <c r="AK30" t="n">
-        <v>-157.380294989923</v>
+        <v>-178.936990790306</v>
       </c>
       <c r="AL30" t="n">
-        <v>-73.1835203395093</v>
+        <v>-73.7911330388922</v>
       </c>
       <c r="AM30" t="n">
-        <v>2195.01109246391</v>
+        <v>2206.32080411441</v>
       </c>
       <c r="AN30" t="n">
-        <v>184.75037233773</v>
+        <v>184.741338531445</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -10665,10 +10773,10 @@
         <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>33.112</v>
+        <v>33.067</v>
       </c>
       <c r="AS30" t="n">
-        <v>52.8453</v>
+        <v>51.768</v>
       </c>
       <c r="AT30" t="n">
         <v>-0.051408</v>
@@ -10680,21 +10788,21 @@
         <v>-0.691527418</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.1953</v>
+        <v>0.222075</v>
       </c>
       <c r="AX30" t="n">
-        <v>1876.30502171875</v>
+        <v>1898.00394021428</v>
       </c>
       <c r="AY30" t="n">
-        <v>316.598450149984</v>
+        <v>314.793067419084</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -10718,13 +10826,13 @@
         <v>0.00531873576798692</v>
       </c>
       <c r="J31" t="n">
-        <v>33634.1693486505</v>
+        <v>33877.4206693275</v>
       </c>
       <c r="K31" t="n">
-        <v>22813.3942648684</v>
+        <v>22992.8464409065</v>
       </c>
       <c r="L31" t="n">
-        <v>2029.86829015562</v>
+        <v>2024.92165780942</v>
       </c>
       <c r="M31" t="n">
         <v>310.870715074303</v>
@@ -10733,28 +10841,28 @@
         <v>75.1961428571429</v>
       </c>
       <c r="O31" t="n">
-        <v>3591.36776333604</v>
+        <v>3689.96355630547</v>
       </c>
       <c r="P31" t="n">
-        <v>5378.04862602595</v>
+        <v>5418.83660930042</v>
       </c>
       <c r="Q31" t="n">
-        <v>2745.91550585515</v>
+        <v>2771.93863237722</v>
       </c>
       <c r="R31" t="n">
-        <v>463.973850877797</v>
+        <v>609.994099501175</v>
       </c>
       <c r="S31" t="n">
         <v>115.322937925207</v>
       </c>
       <c r="T31" t="n">
-        <v>191.853845357623</v>
+        <v>196.443226924582</v>
       </c>
       <c r="U31" t="n">
-        <v>2509.06639335262</v>
+        <v>2516.94052676424</v>
       </c>
       <c r="V31" t="n">
-        <v>206.562781914864</v>
+        <v>206.552681539238</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -10769,7 +10877,7 @@
         <v>37.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>133.9</v>
+        <v>127.6</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -10787,28 +10895,28 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2149.44463063642</v>
+        <v>2171.66261222546</v>
       </c>
       <c r="AH31" t="n">
-        <v>356.997746402807</v>
+        <v>354.497037426154</v>
       </c>
       <c r="AI31" t="n">
-        <v>-3116.31990028589</v>
+        <v>-3137.0184721908</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-1597.04323859381</v>
+        <v>-1607.78157600843</v>
       </c>
       <c r="AK31" t="n">
-        <v>-156.336090019183</v>
+        <v>-182.760127440345</v>
       </c>
       <c r="AL31" t="n">
-        <v>-73.8919818514301</v>
+        <v>-74.6525739363783</v>
       </c>
       <c r="AM31" t="n">
-        <v>2220.01348528944</v>
+        <v>2226.52922306498</v>
       </c>
       <c r="AN31" t="n">
-        <v>185.212248268575</v>
+        <v>185.203191877774</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -10820,10 +10928,10 @@
         <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>33.334</v>
+        <v>33.307</v>
       </c>
       <c r="AS31" t="n">
-        <v>53.974125</v>
+        <v>52.6842</v>
       </c>
       <c r="AT31" t="n">
         <v>-0.074613</v>
@@ -10835,21 +10943,21 @@
         <v>-0.72538577</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.171675</v>
+        <v>0.1953</v>
       </c>
       <c r="AX31" t="n">
-        <v>1901.93860200892</v>
+        <v>1920.069377965</v>
       </c>
       <c r="AY31" t="n">
-        <v>319.117722303653</v>
+        <v>319.291050839969</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -10873,13 +10981,13 @@
         <v>0.00528246336028104</v>
       </c>
       <c r="J32" t="n">
-        <v>33974.522345312</v>
+        <v>34220.2351900146</v>
       </c>
       <c r="K32" t="n">
-        <v>23033.4388074605</v>
+        <v>23214.621873323</v>
       </c>
       <c r="L32" t="n">
-        <v>2040.8916978889</v>
+        <v>2035.9182023489</v>
       </c>
       <c r="M32" t="n">
         <v>313.835316548609</v>
@@ -10888,28 +10996,28 @@
         <v>75.1961428571429</v>
       </c>
       <c r="O32" t="n">
-        <v>3622.370508864</v>
+        <v>3721.81743724505</v>
       </c>
       <c r="P32" t="n">
-        <v>5413.1757256253</v>
+        <v>5454.35505149539</v>
       </c>
       <c r="Q32" t="n">
-        <v>2772.64065691599</v>
+        <v>2798.95682914633</v>
       </c>
       <c r="R32" t="n">
-        <v>468.311157641058</v>
+        <v>615.696428475773</v>
       </c>
       <c r="S32" t="n">
         <v>85.0823596752584</v>
       </c>
       <c r="T32" t="n">
-        <v>191.622440741124</v>
+        <v>196.19325767317</v>
       </c>
       <c r="U32" t="n">
-        <v>2524.17630943851</v>
+        <v>2532.34336351648</v>
       </c>
       <c r="V32" t="n">
-        <v>207.079188869651</v>
+        <v>207.069063243086</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -10924,7 +11032,7 @@
         <v>38.7</v>
       </c>
       <c r="AA32" t="n">
-        <v>133.9</v>
+        <v>127.6</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -10942,28 +11050,28 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2176.11015665922</v>
+        <v>2195.564390209</v>
       </c>
       <c r="AH32" t="n">
-        <v>358.575658685331</v>
+        <v>358.416834279241</v>
       </c>
       <c r="AI32" t="n">
-        <v>-3140.97160419717</v>
+        <v>-3164.18767640365</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-1615.12920029267</v>
+        <v>-1627.48101312322</v>
       </c>
       <c r="AK32" t="n">
-        <v>-155.593128607218</v>
+        <v>-186.930008389538</v>
       </c>
       <c r="AL32" t="n">
-        <v>-74.6093965428009</v>
+        <v>-75.5223491921506</v>
       </c>
       <c r="AM32" t="n">
-        <v>2242.97781152983</v>
+        <v>2249.84808028293</v>
       </c>
       <c r="AN32" t="n">
-        <v>185.675278889246</v>
+        <v>185.666199857468</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -10975,10 +11083,10 @@
         <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>33.726</v>
+        <v>33.711</v>
       </c>
       <c r="AS32" t="n">
-        <v>55.071</v>
+        <v>53.56845</v>
       </c>
       <c r="AT32" t="n">
         <v>-0.097818</v>
@@ -10990,21 +11098,21 @@
         <v>-0.3218514</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.14805</v>
+        <v>0.171675</v>
       </c>
       <c r="AX32" t="n">
-        <v>1923.40097767452</v>
+        <v>1941.75417485585</v>
       </c>
       <c r="AY32" t="n">
-        <v>320.732358648202</v>
+        <v>320.309919568325</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -11028,13 +11136,13 @@
         <v>0.00523852479905496</v>
       </c>
       <c r="J33" t="n">
-        <v>34315.0762587365</v>
+        <v>34563.2520805486</v>
       </c>
       <c r="K33" t="n">
-        <v>23251.4738108507</v>
+        <v>23434.3719593246</v>
       </c>
       <c r="L33" t="n">
-        <v>2046.64306409843</v>
+        <v>2041.65555292291</v>
       </c>
       <c r="M33" t="n">
         <v>316.829129446497</v>
@@ -11043,28 +11151,28 @@
         <v>75.1961428571429</v>
       </c>
       <c r="O33" t="n">
-        <v>3653.24368054323</v>
+        <v>3753.53818707383</v>
       </c>
       <c r="P33" t="n">
-        <v>5447.80859103241</v>
+        <v>5489.39569550016</v>
       </c>
       <c r="Q33" t="n">
-        <v>2799.69825793831</v>
+        <v>2826.31248358626</v>
       </c>
       <c r="R33" t="n">
-        <v>472.689010288367</v>
+        <v>620.498876538429</v>
       </c>
       <c r="S33" t="n">
         <v>50.6890505411461</v>
       </c>
       <c r="T33" t="n">
-        <v>192.885105061588</v>
+        <v>197.557220327612</v>
       </c>
       <c r="U33" t="n">
-        <v>2541.58265628632</v>
+        <v>2549.71011858832</v>
       </c>
       <c r="V33" t="n">
-        <v>207.596886841825</v>
+        <v>207.586735901194</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -11079,7 +11187,7 @@
         <v>39.7</v>
       </c>
       <c r="AA33" t="n">
-        <v>133.9</v>
+        <v>127.6</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -11097,28 +11205,28 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2210.2161922716</v>
+        <v>2232.55499411875</v>
       </c>
       <c r="AH33" t="n">
-        <v>365.20640021081</v>
+        <v>365.436265662356</v>
       </c>
       <c r="AI33" t="n">
-        <v>-3163.51171755951</v>
+        <v>-3189.27096330564</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-1632.22206089396</v>
+        <v>-1646.20619321094</v>
       </c>
       <c r="AK33" t="n">
-        <v>-154.39609561683</v>
+        <v>-190.659970940819</v>
       </c>
       <c r="AL33" t="n">
-        <v>-75.2322333781871</v>
+        <v>-76.300923203071</v>
       </c>
       <c r="AM33" t="n">
-        <v>2265.53601167434</v>
+        <v>2272.67670094338</v>
       </c>
       <c r="AN33" t="n">
-        <v>186.139467086469</v>
+        <v>186.130365357112</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -11130,10 +11238,10 @@
         <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>34.295</v>
+        <v>34.28</v>
       </c>
       <c r="AS33" t="n">
-        <v>56.3688</v>
+        <v>54.653625</v>
       </c>
       <c r="AT33" t="n">
         <v>-0.082501</v>
@@ -11145,21 +11253,21 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.124425</v>
+        <v>0.14805</v>
       </c>
       <c r="AX33" t="n">
-        <v>1948.44377739026</v>
+        <v>1967.47586353237</v>
       </c>
       <c r="AY33" t="n">
-        <v>323.19270963607</v>
+        <v>322.546573048761</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -11183,13 +11291,13 @@
         <v>0.00520317743921583</v>
       </c>
       <c r="J34" t="n">
-        <v>34657.6393397919</v>
+        <v>34908.2926695519</v>
       </c>
       <c r="K34" t="n">
-        <v>23476.9441092875</v>
+        <v>23661.6158270609</v>
       </c>
       <c r="L34" t="n">
-        <v>2050.39853806318</v>
+        <v>2045.40187508747</v>
       </c>
       <c r="M34" t="n">
         <v>319.8524416</v>
@@ -11198,28 +11306,28 @@
         <v>75.1961428571429</v>
       </c>
       <c r="O34" t="n">
-        <v>3683.98816476245</v>
+        <v>3785.12671651503</v>
       </c>
       <c r="P34" t="n">
-        <v>5530.33475107243</v>
+        <v>5572.3334479222</v>
       </c>
       <c r="Q34" t="n">
-        <v>2827.38715611674</v>
+        <v>2854.3057827196</v>
       </c>
       <c r="R34" t="n">
-        <v>477.107787849569</v>
+        <v>625.338783820155</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>28.4306176015575</v>
       </c>
       <c r="T34" t="n">
-        <v>192.593334023393</v>
+        <v>197.242041706267</v>
       </c>
       <c r="U34" t="n">
-        <v>2560.08016324453</v>
+        <v>2568.16679225807</v>
       </c>
       <c r="V34" t="n">
-        <v>208.115879058929</v>
+        <v>208.105702740947</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -11234,7 +11342,7 @@
         <v>39.7</v>
       </c>
       <c r="AA34" t="n">
-        <v>134.9</v>
+        <v>128.6</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -11252,28 +11360,28 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2243.80027919646</v>
+        <v>2268.93037486315</v>
       </c>
       <c r="AH34" t="n">
-        <v>373.030059953625</v>
+        <v>373.867091412813</v>
       </c>
       <c r="AI34" t="n">
-        <v>-3198.22734415068</v>
+        <v>-3226.55567396658</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-1649.45008021301</v>
+        <v>-1665.08547738852</v>
       </c>
       <c r="AK34" t="n">
-        <v>-154.659688545149</v>
+        <v>-195.864597068157</v>
       </c>
       <c r="AL34" t="n">
-        <v>-75.5053445123002</v>
+        <v>-76.7289912599466</v>
       </c>
       <c r="AM34" t="n">
-        <v>2280.35374252244</v>
+        <v>2287.6111802536</v>
       </c>
       <c r="AN34" t="n">
-        <v>186.604815754185</v>
+        <v>186.595691270505</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -11285,10 +11393,10 @@
         <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>34.837</v>
+        <v>34.825</v>
       </c>
       <c r="AS34" t="n">
-        <v>57.2526</v>
+        <v>55.3248</v>
       </c>
       <c r="AT34" t="n">
         <v>-0.067184</v>
@@ -11300,69 +11408,169 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.1008</v>
+        <v>0.124425</v>
       </c>
       <c r="AX34" t="n">
-        <v>1975.40353322183</v>
+        <v>1995.46028356868</v>
       </c>
       <c r="AY34" t="n">
-        <v>327.107219681829</v>
+        <v>326.748876475627</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>86</v>
-      </c>
-      <c r="B35"/>
-      <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
-      <c r="AG35"/>
-      <c r="AH35"/>
-      <c r="AI35"/>
-      <c r="AJ35"/>
-      <c r="AK35"/>
-      <c r="AL35"/>
-      <c r="AM35"/>
-      <c r="AN35"/>
-      <c r="AO35"/>
-      <c r="AP35"/>
-      <c r="AQ35"/>
-      <c r="AR35"/>
-      <c r="AS35"/>
-      <c r="AT35"/>
-      <c r="AU35"/>
-      <c r="AV35"/>
-      <c r="AW35"/>
-      <c r="AX35"/>
-      <c r="AY35"/>
+        <v>87</v>
+      </c>
+      <c r="B35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.00576802715135072</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.00741442094618439</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.00741442094618439</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.00741442094618439</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00533209290372461</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.00518825436858217</v>
+      </c>
+      <c r="J35" t="n">
+        <v>35249.3870465401</v>
+      </c>
+      <c r="K35" t="n">
+        <v>23882.8849228737</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2053.28720486566</v>
+      </c>
+      <c r="M35" t="n">
+        <v>312.905543677275</v>
+      </c>
+      <c r="N35" t="n">
+        <v>75.1961428571429</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3817.00876784</v>
+      </c>
+      <c r="P35" t="n">
+        <v>5609.46393518282</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2882.00396607354</v>
+      </c>
+      <c r="R35" t="n">
+        <v>630.216442503827</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10.8884618270169</v>
+      </c>
+      <c r="T35" t="n">
+        <v>197.089886509756</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2587.71443212373</v>
+      </c>
+      <c r="V35" t="n">
+        <v>208.625966997799</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2306.28413399849</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>382.130773934261</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>-3265.65360445851</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>-1681.65720430216</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>-201.215145151618</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>-77.1986541436051</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>2303.53530895948</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>187.062180498681</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>35.287</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>55.83015</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>-0.051867</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>2025.75012596761</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>332.966467189951</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11410,129 +11618,129 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AG1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AI1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AJ1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AK1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AL1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AM1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AN1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AO1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AP1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AQ1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AR1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AS1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AT1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AU1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AV1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AW1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AX1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AY1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="n">
@@ -11685,7 +11893,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="n">
@@ -11838,7 +12046,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4"/>
       <c r="C4" t="n">
@@ -11991,7 +12199,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B5"/>
       <c r="C5" t="n">
@@ -12144,7 +12352,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6"/>
       <c r="C6" t="n">
@@ -12297,7 +12505,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7"/>
       <c r="C7" t="n">
@@ -12450,7 +12658,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8"/>
       <c r="C8" t="n">
@@ -12603,7 +12811,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9"/>
       <c r="C9" t="n">
@@ -12756,7 +12964,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10"/>
       <c r="C10" t="n">
@@ -12909,7 +13117,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11"/>
       <c r="C11" t="n">
@@ -13062,7 +13270,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12"/>
       <c r="C12" t="n">
@@ -13215,7 +13423,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13"/>
       <c r="C13" t="n">
@@ -13368,7 +13576,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14"/>
       <c r="C14" t="n">
@@ -13521,7 +13729,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15"/>
       <c r="C15" t="n">
@@ -13674,7 +13882,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16"/>
       <c r="C16" t="n">
@@ -13827,7 +14035,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17"/>
       <c r="C17" t="n">
@@ -13980,7 +14188,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18"/>
       <c r="C18" t="n">
@@ -14133,7 +14341,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19"/>
       <c r="C19" t="n">
@@ -14286,7 +14494,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20"/>
       <c r="C20" t="n">
@@ -14439,7 +14647,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21"/>
       <c r="C21" t="n">
@@ -14592,7 +14800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22"/>
       <c r="C22" t="n">
@@ -14745,7 +14953,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B23"/>
       <c r="C23" t="n">
@@ -14898,7 +15106,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B24"/>
       <c r="C24" t="n">
@@ -15051,7 +15259,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B25"/>
       <c r="C25" t="n">
@@ -15204,7 +15412,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B26"/>
       <c r="C26" t="n">
@@ -15253,7 +15461,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>144.578924869627</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -15310,7 +15518,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>-4.81929749565398</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -15357,38 +15565,38 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27"/>
       <c r="C27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00348688103876402</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.029545611335792</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0112475792968861</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0259970309191944</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00570497762719823</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>233.182902746801</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>172.3136386435</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>-4.82590350581995</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -15397,28 +15605,28 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>95.0617119369399</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>43.0759268320098</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>24.8272272003901</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>108.568724234095</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>4.482433126703</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>29.1806839670198</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.00999999999999091</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -15430,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.300000000000004</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>-6.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -15448,31 +15656,31 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>38.07639287548</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>-11.294981275389</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>-5.16911121984003</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-2.97926726404989</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>-8.43825497012398</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.1494144375568</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>6.56565389258003</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>-0.00225000000000364</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -15484,10 +15692,10 @@
         <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>-0.0600000000000023</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>-0.31185</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
         <v>0</v>
@@ -15499,18 +15707,18 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.03465</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.5671883969801</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>-2.541370786963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28"/>
       <c r="C28" t="n">
@@ -15535,13 +15743,13 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>235.895810276801</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>174.265829450003</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>-4.86364344904018</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -15550,28 +15758,28 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>95.9813124361699</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>69.5122281505201</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>25.15470056908</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>105.557342268742</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>4.536109136341</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>6.59136084438978</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.0100250000000131</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -15586,7 +15794,7 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>-6.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -15604,28 +15812,28 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>18.4656947709</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.48903166587797</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>-13.5105785978999</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-5.99783133234018</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>-11.956833045749</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.300618075434713</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>8.04871008255986</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>-0.00450562500000729</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -15637,10 +15845,10 @@
         <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>-0.0510000000000019</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>-0.581175000000002</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
@@ -15652,18 +15860,18 @@
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.029925</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>12.72196972044</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>-1.98133866213999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29"/>
       <c r="C29" t="n">
@@ -15688,13 +15896,13 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>238.402379901498</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>176.104998683597</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>-4.89373645515002</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -15703,28 +15911,28 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>96.8285803170897</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>70.0114501221005</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>25.4619343732502</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>143.328013948518</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>4.62731799482302</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>6.92559334226007</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.0100500624999995</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -15739,7 +15947,7 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>-6.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -15757,28 +15965,28 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>19.3215175770101</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.22407659568302</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>-19.3273970026403</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-7.56362982510018</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>-16.734433510699</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>-0.454862008595597</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>9.60696858458004</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>-0.0067668890629875</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -15790,10 +15998,10 @@
         <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>-0.0480000000000018</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>-0.836325000000002</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
         <v>0</v>
@@ -15805,18 +16013,18 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.02835</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>17.0693111752598</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>-1.70592142811103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B30"/>
       <c r="C30" t="n">
@@ -15841,13 +16049,13 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>240.828303373099</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>177.8105969672</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>-4.92116680866002</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -15856,28 +16064,28 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>97.7132567267099</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>40.4003133807901</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>25.7410875283999</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>144.66786869052</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>4.58252072362203</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>7.56774695969034</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.0100751876569802</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -15892,7 +16100,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>-6.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -15910,28 +16118,28 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>20.57603253452</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.442050234617966</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>-20.0047009192999</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-9.14327829436979</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>-21.556695800383</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.607612699382898</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>11.3097116505</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>-0.00903380628500372</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -15943,10 +16151,10 @@
         <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>-0.0450000000000017</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>-1.0773</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
@@ -15958,18 +16166,18 @@
         <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.026775</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>21.6989184955301</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>-1.80538273089996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B31"/>
       <c r="C31" t="n">
@@ -15994,13 +16202,13 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>243.251320676995</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>179.452176038103</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>-4.94663234619998</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -16009,28 +16217,28 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>98.59579296943</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>40.7879832744693</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>26.02312652207</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>146.020248623378</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>4.58938156695902</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>7.87413341162028</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.0101003756259956</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -16045,7 +16253,7 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>-6.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -16063,28 +16271,28 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>22.2179815890404</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>-2.50070897665302</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>-20.6985719049098</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-10.73833741462</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>-26.424037421162</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.7605920849482</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>6.5157377755404</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>-0.00905639080099263</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -16096,10 +16304,10 @@
         <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>-0.027000000000001</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>-1.289925</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
@@ -16111,18 +16319,18 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.023625</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>18.13077595608</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.173328536315978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B32"/>
       <c r="C32" t="n">
@@ -16147,13 +16355,13 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>245.712844702604</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>181.1830658625</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>-4.97349553999993</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -16162,28 +16370,28 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>99.4469283810499</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>41.17932587009</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>26.3161722303403</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>147.385270834715</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>4.570816932046</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>8.16705407797008</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.0101256265650136</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -16198,7 +16406,7 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>-6.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -16216,28 +16424,28 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>19.4542335497799</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>-0.158824406089991</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>-23.21607220648</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-12.35181283055</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>-31.33687978232</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>-0.912952649349705</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>6.87026875309994</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>-0.0090790317779863</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -16249,10 +16457,10 @@
         <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>-0.0150000000000006</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>-1.50255</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
         <v>0</v>
@@ -16264,18 +16472,18 @@
         <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.023625</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>18.35319718133</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>-0.422439079877051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B33"/>
       <c r="C33" t="n">
@@ -16300,13 +16508,13 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>248.175821812096</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>182.898148473898</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>-4.98751117552001</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -16315,28 +16523,28 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>100.2945065306</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>41.5871044677506</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>26.6142256479502</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>147.809866250062</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>4.67211526602398</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>8.12746230199991</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.0101509406310072</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -16351,7 +16559,7 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>-6.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -16369,28 +16577,28 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>22.3388018471501</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.229865451546004</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>-25.7592457461301</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-13.9841323169801</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>-36.263875323989</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>-1.06868982488389</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>7.14068926904019</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>-0.00910172935701326</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -16402,10 +16610,10 @@
         <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>-0.0150000000000006</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>-1.715175</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
@@ -16417,18 +16625,18 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.023625</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>19.0320861421101</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>-0.646136587309002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B34"/>
       <c r="C34" t="n">
@@ -16453,13 +16661,13 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>250.653329759996</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>184.671717773403</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>-4.9966629757098</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -16468,28 +16676,28 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>101.13855175258</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>41.9986968497706</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>26.9186266028601</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>148.230995970586</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>28.4306176015575</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>4.648707682874</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>8.08662901354</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>-0.0101763179820011</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -16504,7 +16712,7 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>-6.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -16522,28 +16730,28 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>25.1300956666901</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.837031459187983</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>-28.3283298158999</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-15.63539717551</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>-41.204908523008</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>-1.2236467476464</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>7.25743773116028</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>-0.00912448368001151</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -16555,10 +16763,10 @@
         <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>-0.0120000000000005</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>-1.9278</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
@@ -16570,69 +16778,167 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.023625</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>20.0567503468501</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>-0.358343206201994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B35"/>
-      <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
-      <c r="AG35"/>
-      <c r="AH35"/>
-      <c r="AI35"/>
-      <c r="AJ35"/>
-      <c r="AK35"/>
-      <c r="AL35"/>
-      <c r="AM35"/>
-      <c r="AN35"/>
-      <c r="AO35"/>
-      <c r="AP35"/>
-      <c r="AQ35"/>
-      <c r="AR35"/>
-      <c r="AS35"/>
-      <c r="AT35"/>
-      <c r="AU35"/>
-      <c r="AV35"/>
-      <c r="AW35"/>
-      <c r="AX35"/>
-      <c r="AY35"/>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
